--- a/data/trans_orig/IP07A11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28437</t>
+          <t>28958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>28511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54565</t>
+          <t>55038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,22%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>49040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56808</t>
+          <t>56383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>78335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>101685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141634</t>
+          <t>140844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175136</t>
+          <t>173671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91189</t>
+          <t>91866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114530</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99634</t>
+          <t>99329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123603</t>
+          <t>124616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195976</t>
+          <t>196711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231771</t>
+          <t>232671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>23360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40245</t>
+          <t>39504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53017</t>
+          <t>51071</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76044</t>
+          <t>75407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53068</t>
+          <t>53553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38324</t>
+          <t>38449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>51082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69037</t>
+          <t>68927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>124437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123782</t>
+          <t>125182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153070</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>226530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>268509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>141077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>170559</t>
+          <t>170483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145222</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>293619</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>335958</t>
+          <t>339033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62311</t>
+          <t>62198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81324</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>34997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46943</t>
+          <t>47669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>63872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>39940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95434</t>
+          <t>95938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>119907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113384</t>
+          <t>114389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139507</t>
+          <t>137672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215103</t>
+          <t>216730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249492</t>
+          <t>251739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69814</t>
+          <t>69269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93005</t>
+          <t>92204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,82 +4501,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>83503</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71261</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94555</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>36,51%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>164317</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>147309</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>182114</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>37,79%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>33,87%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83503</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72037</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95479</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>31,5%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>41,74%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>164317</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>147373</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>181173</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>37,79%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41129</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30621</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43494</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>21998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>34106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>55192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>73408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40742</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58976</t>
+          <t>60423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>157065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187235</t>
+          <t>186000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>165792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>194485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332317</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373725</t>
+          <t>374374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107480</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137045</t>
+          <t>137987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>110293</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>139073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225573</t>
+          <t>226943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>266584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36578</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110009</t>
+          <t>110733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135873</t>
+          <t>136351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116033</t>
+          <t>115013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143924</t>
+          <t>142477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233771</t>
+          <t>234582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269609</t>
+          <t>269466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76864</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102569</t>
+          <t>102140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79134</t>
+          <t>80620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106504</t>
+          <t>106573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166635</t>
+          <t>164967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201986</t>
+          <t>201598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>40816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40228</t>
+          <t>40127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62307</t>
+          <t>62583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,82 +7686,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8587</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>8647</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>4230</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>14140</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8553</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>8647</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>4417</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>14424</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>50718</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69919</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90651</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34086</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>63562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158193</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>189781</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>173250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204750</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>341192</t>
+          <t>340281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>382552</t>
+          <t>384763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112452</t>
+          <t>113727</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>143683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>122059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152413</t>
+          <t>151755</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,47 +8859,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>264724</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>242439</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>285390</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>33,79%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>42,18%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>264724</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>243973</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>285832</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>36,89%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23350</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18161</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29255</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23114</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17530</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28958</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18202</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29312</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>45,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23350</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17932</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28511</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>53770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19824</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14094</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25081</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21210</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15580</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27122</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15732</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26879</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19824</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14513</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25103</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49040</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5617</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2657</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9949</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10391</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,08%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6755</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -1066,102 +1066,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3667</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90056</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78851</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103456</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66955</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56383</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78002</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>56794</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>78419</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90056</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>78335</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>101685</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140844</t>
+          <t>142490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173671</t>
+          <t>173507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>111690</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100436</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>123776</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>103107</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91866</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113885</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>91620</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>113655</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>50,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>111690</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>99329</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>124616</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,94%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196711</t>
+          <t>199023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232671</t>
+          <t>230565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33030</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25338</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42097</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>30814</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23360</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39504</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22461</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39012</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>15,14%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33030</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>25743</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42572</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>53479</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75407</t>
+          <t>77158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5739</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2125</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6477</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5771</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>9140</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4631</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>9569</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>462</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2318</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4123</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>203463</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>203463</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>203463</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24861</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18742</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30860</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19268</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13332</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25542</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13515</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25802</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,82%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24861</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18923</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30852</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>35843</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>53739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28281</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34594</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>31622</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24815</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38449</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25261</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>38416</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>47,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>28281</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22355</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34554</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>46,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68927</t>
+          <t>70439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3672</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12089</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14601</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9710</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20602</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10045</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>20818</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>21,84%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,82%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7252</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29715</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4438</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5384</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4176</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>138268</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>122846</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>153392</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>35,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>109337</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>96092</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>124437</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>96937</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>123816</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>34,06%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>138268</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>125182</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>154451</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>40,01%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226530</t>
+          <t>225917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>268509</t>
+          <t>267599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>159796</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>144280</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>175230</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,71%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>155939</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>141077</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>170483</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>141454</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>169372</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>48,58%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>159796</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>144566</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>173229</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>46,24%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296817</t>
+          <t>295525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>339033</t>
+          <t>338524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,79%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>43658</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>34941</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>54848</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>51032</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>40593</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>62198</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>41336</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>62604</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>15,9%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>19,38%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>43658</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>34187</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>54347</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>79959</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108915</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>4221</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8497</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3225,102 +3225,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>462</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4296</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>320991</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26663</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21078</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32550</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28825</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22385</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34997</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23003</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35216</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26663</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21027</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32095</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47669</t>
+          <t>47003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>62857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13585</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8447</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19504</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18454</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12462</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24677</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24437</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13585</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9036</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19348</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>24745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -3912,67 +3912,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>4374</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9133</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>5005</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9804</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9528</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,43%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4374</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9117</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -4020,72 +4020,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4804</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>798</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4342</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4306</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4364</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>125979</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>113460</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137312</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107041</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95938</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>119907</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>95185</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>118480</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>125979</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>114389</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>137672</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216730</t>
+          <t>216002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251739</t>
+          <t>250230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83503</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72394</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95140</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80814</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69269</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>92204</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69208</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>92785</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83503</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71261</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>94555</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>147985</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182114</t>
+          <t>180775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22204</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10950</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24571</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11464</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9122</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21170</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6986</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1292</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3987</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7425</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4815,92 +4815,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1294</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>228723</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206144</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206144</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206144</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>228723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28102</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34498</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36906</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30063</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43658</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30341</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43109</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>28102</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>21998</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34106</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>48,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55192</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73408</t>
+          <t>75114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26644</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20473</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32544</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23379</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16918</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29977</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17660</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29913</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26644</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>20594</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32200</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60423</t>
+          <t>59068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7510</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3134</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7664</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3187</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1139</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6718</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>180743</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>165220</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>195602</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>49,69%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>172772</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>157065</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>186000</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>158240</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>187476</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>53,55%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>180743</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>165792</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>194485</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333438</t>
+          <t>332881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374374</t>
+          <t>374876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>123732</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>109802</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139276</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33,02%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>122647</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>109631</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>137987</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>108286</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>136438</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>38,01%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>42,77%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>123732</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>110293</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>139073</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>226943</t>
+          <t>225632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266584</t>
+          <t>266035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22234</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15572</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>30980</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>25136</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>18132</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>33911</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17671</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>34223</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22234</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>15609</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>30594</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -6066,107 +6066,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2090</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>6595</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>11777</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4504</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8633</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>6595</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>3121</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>11374</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6179,107 +6179,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>1294</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4194</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>322645</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>322645</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>322645</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6645,67 +6645,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>15105</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10593</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20189</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>14937</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10107</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19545</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10787</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19899</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15105</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10442</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36478</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17999</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12932</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22925</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11488</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7247</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16193</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7390</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15961</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12991</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22745</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9265</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3534</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7816</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -6979,107 +6979,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3246</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>129587</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>116648</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143260</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>122598</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>110733</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>136351</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>109682</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>135721</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>129587</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>115013</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>142477</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234582</t>
+          <t>233925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269466</t>
+          <t>270715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>93603</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81153</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106942</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89360</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76304</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>102140</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77344</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>102489</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>93603</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80620</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>106573</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164967</t>
+          <t>166447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201598</t>
+          <t>201411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19250</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13039</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26437</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31184</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22779</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40816</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23119</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>41140</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,48%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19250</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13340</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27563</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>62765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7792</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5115</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10411</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8587</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3843</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1684</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6135</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6444</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3979</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>246662</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>249942</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>249942</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>249942</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>246662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>43221</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35718</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>50182</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>37240</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30442</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44464</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30232</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44539</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>43221</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36083</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50718</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>70435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>90345</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25681</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18608</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32689</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>26593</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19347</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33416</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19820</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>34159</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,92%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>25681</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19227</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32535</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63562</t>
+          <t>61854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4232</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13320</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9774</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5602</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15240</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5369</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15076</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7974</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4291</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13659</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -8348,102 +8348,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>792</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5104</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3607</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1427</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5273</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3438</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>2765</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>187914</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>170712</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>204290</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>47,24%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>56,53%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>174776</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>160545</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>190763</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>159579</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>189768</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>49,07%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>45,08%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>53,56%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>187914</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>173250</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>202594</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>340281</t>
+          <t>339626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>384763</t>
+          <t>384035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>137283</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>121414</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>153585</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>127441</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>113727</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>143683</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>112862</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>142606</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>35,78%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>137283</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>122059</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>151755</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>242439</t>
+          <t>244053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>285390</t>
+          <t>285621</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22339</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>39470</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>45719</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>36606</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>57601</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>35520</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>56100</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>30759</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>21977</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>39776</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>63062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91134</t>
+          <t>90575</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4167</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>6536</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>12156</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12165</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8908</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -9143,67 +9143,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1684</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5723</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4336</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>356155</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>356155</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>356155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
